--- a/resources.xlsx
+++ b/resources.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sivane\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ADF2CE4-802B-4FF0-AAAE-E5D88FB6BA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E4262E-1620-4316-9C04-910C5BF88702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{72F27D78-0761-444B-B507-399DE519242A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72F27D78-0761-444B-B507-399DE519242A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -169,7 +169,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -216,9 +216,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -256,7 +256,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -362,7 +362,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -504,7 +504,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -513,17 +513,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C41FC6-438C-4BD4-A2E9-CE129E12FD15}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.58203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.58203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -543,7 +543,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -563,7 +563,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -574,16 +574,16 @@
         <v>21</v>
       </c>
       <c r="D3" s="1">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="E3" t="s">
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -603,7 +603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -623,7 +623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -643,7 +643,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -683,7 +683,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -703,7 +703,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -723,7 +723,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>35</v>
       </c>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sivane\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E4262E-1620-4316-9C04-910C5BF88702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1A65E4-53EF-4336-A743-70D6F1A925C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72F27D78-0761-444B-B507-399DE519242A}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{72F27D78-0761-444B-B507-399DE519242A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="44">
   <si>
     <t>worker_name</t>
   </si>
@@ -159,6 +159,18 @@
   </si>
   <si>
     <t xml:space="preserve">מנהל תחזוקה </t>
+  </si>
+  <si>
+    <t>ורד גדנקן</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מנהלת בדיקות </t>
+  </si>
+  <si>
+    <t>אחראית גם על מוצר מעסיקים</t>
+  </si>
+  <si>
+    <t>אלמוג לוזון</t>
   </si>
 </sst>
 </file>
@@ -169,7 +181,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -216,9 +228,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -256,7 +268,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -362,7 +374,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -504,7 +516,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -512,18 +524,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C41FC6-438C-4BD4-A2E9-CE129E12FD15}">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.4140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.4140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.58203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -543,7 +555,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -563,7 +575,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -583,7 +595,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -603,7 +615,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -623,7 +635,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -643,7 +655,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -663,7 +675,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -683,7 +695,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -703,7 +715,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -723,7 +735,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -741,6 +753,43 @@
       </c>
       <c r="F11" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1A65E4-53EF-4336-A743-70D6F1A925C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7BDCA04-09B5-4C72-8BD1-40C9AC6D2826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{72F27D78-0761-444B-B507-399DE519242A}"/>
+    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="10060" xr2:uid="{72F27D78-0761-444B-B507-399DE519242A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="50">
   <si>
     <t>worker_name</t>
   </si>
@@ -171,12 +171,33 @@
   </si>
   <si>
     <t>אלמוג לוזון</t>
+  </si>
+  <si>
+    <t>יעל ויישנשטרן</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בודקת </t>
+  </si>
+  <si>
+    <t>סיון פרידמן</t>
+  </si>
+  <si>
+    <t>פעיל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">דלק </t>
+  </si>
+  <si>
+    <t>דנאל</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -207,9 +228,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -524,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C41FC6-438C-4BD4-A2E9-CE129E12FD15}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.58203125" bestFit="1" customWidth="1"/>
@@ -560,116 +582,101 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
+        <v>0.25</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>
       </c>
       <c r="D3" s="1">
-        <v>0</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
+        <v>0.5</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
+        <v>0.2</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>29</v>
+        <v>21</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D7" s="1">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
@@ -677,79 +684,79 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D10" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="D11" s="1">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
@@ -757,19 +764,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="D12" s="1">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
@@ -777,19 +784,136 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>7</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
         <v>43</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C18" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D18" s="1">
         <v>0</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F18" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7BDCA04-09B5-4C72-8BD1-40C9AC6D2826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1031EBCA-401B-42FA-9360-34742AAE2096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="10060" xr2:uid="{72F27D78-0761-444B-B507-399DE519242A}"/>
+    <workbookView xWindow="20" yWindow="380" windowWidth="19180" windowHeight="10060" xr2:uid="{72F27D78-0761-444B-B507-399DE519242A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="52">
   <si>
     <t>worker_name</t>
   </si>
@@ -189,6 +189,12 @@
   </si>
   <si>
     <t>דנאל</t>
+  </si>
+  <si>
+    <t>ללא</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ללא </t>
   </si>
 </sst>
 </file>
@@ -590,6 +596,9 @@
       <c r="D2" s="1">
         <v>0.25</v>
       </c>
+      <c r="E2" t="s">
+        <v>50</v>
+      </c>
       <c r="F2" t="s">
         <v>47</v>
       </c>
@@ -607,6 +616,9 @@
       <c r="D3" s="1">
         <v>0.5</v>
       </c>
+      <c r="E3" t="s">
+        <v>50</v>
+      </c>
       <c r="F3" t="s">
         <v>47</v>
       </c>
@@ -624,6 +636,9 @@
       <c r="D4" s="1">
         <v>0.2</v>
       </c>
+      <c r="E4" t="s">
+        <v>50</v>
+      </c>
       <c r="F4" t="s">
         <v>47</v>
       </c>
@@ -641,6 +656,9 @@
       <c r="D5" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
+      <c r="E5" t="s">
+        <v>50</v>
+      </c>
       <c r="F5" t="s">
         <v>47</v>
       </c>
@@ -658,6 +676,9 @@
       <c r="D6" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
+      <c r="E6" t="s">
+        <v>50</v>
+      </c>
       <c r="F6" t="s">
         <v>47</v>
       </c>
@@ -895,6 +916,9 @@
       <c r="D18" s="1">
         <v>0</v>
       </c>
+      <c r="E18" t="s">
+        <v>50</v>
+      </c>
       <c r="F18" t="s">
         <v>14</v>
       </c>
@@ -911,6 +935,9 @@
       </c>
       <c r="D19" s="1">
         <v>0.05</v>
+      </c>
+      <c r="E19" t="s">
+        <v>51</v>
       </c>
       <c r="F19" t="s">
         <v>11</v>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1031EBCA-401B-42FA-9360-34742AAE2096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C3DFF0-FAD9-40B8-BD1E-959D334585AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="380" windowWidth="19180" windowHeight="10060" xr2:uid="{72F27D78-0761-444B-B507-399DE519242A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{72F27D78-0761-444B-B507-399DE519242A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="53">
   <si>
     <t>worker_name</t>
   </si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t xml:space="preserve">ללא </t>
+  </si>
+  <si>
+    <t xml:space="preserve">אסתי רדליך </t>
   </si>
 </sst>
 </file>
@@ -552,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C41FC6-438C-4BD4-A2E9-CE129E12FD15}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.58203125" bestFit="1" customWidth="1"/>
@@ -943,6 +946,26 @@
         <v>11</v>
       </c>
     </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/resources.xlsx
+++ b/resources.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C3DFF0-FAD9-40B8-BD1E-959D334585AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DE49D8-F72F-4774-9A01-50FB2FC40755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{72F27D78-0761-444B-B507-399DE519242A}"/>
   </bookViews>
@@ -68,9 +68,6 @@
     <t>אלישבע שליסל</t>
   </si>
   <si>
-    <t>מפתחת backend</t>
-  </si>
-  <si>
     <t>worker_status</t>
   </si>
   <si>
@@ -92,12 +89,6 @@
     <t xml:space="preserve">דבורה קופמן </t>
   </si>
   <si>
-    <t>מפתחת frontend</t>
-  </si>
-  <si>
-    <t>מפתחת fullstack</t>
-  </si>
-  <si>
     <t xml:space="preserve">השמה אצל לקוח </t>
   </si>
   <si>
@@ -107,9 +98,6 @@
     <t>מנהלת פרויקטים</t>
   </si>
   <si>
-    <t xml:space="preserve">מתפקדת כמומחית תוכן בפרויקט </t>
-  </si>
-  <si>
     <t xml:space="preserve">סתיו ברנשטיין </t>
   </si>
   <si>
@@ -119,9 +107,6 @@
     <t>אריק ישראל</t>
   </si>
   <si>
-    <t>מפתח frontend</t>
-  </si>
-  <si>
     <t>אחראית גם על שירותי הלקוח</t>
   </si>
   <si>
@@ -134,9 +119,6 @@
     <t xml:space="preserve">תומכת גם במודול מידע במעסיקים </t>
   </si>
   <si>
-    <t>מוביל תהליכי Ci-CD</t>
-  </si>
-  <si>
     <t>מכירה את הפעילות מקצה לקצה</t>
   </si>
   <si>
@@ -198,6 +180,24 @@
   </si>
   <si>
     <t xml:space="preserve">אסתי רדליך </t>
+  </si>
+  <si>
+    <t>מפתחת Backend</t>
+  </si>
+  <si>
+    <t>מפתחת Fullstack</t>
+  </si>
+  <si>
+    <t>מפתח Frontend</t>
+  </si>
+  <si>
+    <t>מפתחת Frontend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מומחית תוכן בפרויקט </t>
+  </si>
+  <si>
+    <t>מוביל תהליכי CI-CD</t>
   </si>
 </sst>
 </file>
@@ -583,7 +583,7 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -591,19 +591,19 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1">
         <v>0.25</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -611,79 +611,79 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1">
         <v>0.5</v>
       </c>
       <c r="E3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1">
         <v>0.2</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="E5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D6" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="E6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -694,16 +694,16 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1">
         <v>0.33</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -711,19 +711,19 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -731,39 +731,39 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
         <v>13</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -771,19 +771,19 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D11" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -791,19 +791,19 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -811,119 +811,119 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D16" s="1">
         <v>0.1</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D17" s="1">
         <v>0.1</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E18" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -931,39 +931,39 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
         <v>44</v>
       </c>
-      <c r="C19" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="E19" t="s">
-        <v>51</v>
-      </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D20" s="1">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F20" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
